--- a/results/meta_analysis/tables/meta_analysis_outputs.xlsx
+++ b/results/meta_analysis/tables/meta_analysis_outputs.xlsx
@@ -9,13 +9,14 @@
     <sheet name="Meta_Analysis_Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Study_Level_Effects" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Figure_Manifest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Failures" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Analysis_Registry" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Study_Label_Crosswalk" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t xml:space="preserve">analysis_group</t>
   </si>
@@ -59,6 +60,18 @@
     <t xml:space="preserve">control_label</t>
   </si>
   <si>
+    <t xml:space="preserve">analysis_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis_purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_workspace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_r29_summary</t>
+  </si>
+  <si>
     <t xml:space="preserve">source_dataset</t>
   </si>
   <si>
@@ -68,6 +81,81 @@
     <t xml:space="preserve">forest_plot_pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">meta_analysis_ready_primary_rct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random-effects REML + Hartung-Knapp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGLT2i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main_analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_primary_rct.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_meta_analysis_ready_primary_rct.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_meta_analysis_ready_primary_rct.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meta_analysis_ready_secondary_observational</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_secondary_observational.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_meta_analysis_ready_secondary_observational.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_meta_analysis_ready_secondary_observational.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meta_analysis_ready_sensitivity_rct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_sensitivity_rct.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_meta_analysis_ready_sensitivity_rct.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_meta_analysis_ready_sensitivity_rct.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creatinine_only_aki_sensitivity_analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">additional_analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/additional_analysis/AA_20260816_110220_creatinine_only_aki_sensitivity_analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/additional_analysis/AA_20260816_110220_creatinine_only_aki_sensitivity_analysis/meta_analysis_summary.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/additional_analysis/AA_20260816_110220_creatinine_only_aki_sensitivity_analysis/additional_analysis_meta_analysis_ready.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_creatinine_only_aki_sensitivity_analysis.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/results/meta_analysis/figures/forest_creatinine_only_aki_sensitivity_analysis.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">study_label</t>
   </si>
   <si>
@@ -95,6 +183,72 @@
     <t xml:space="preserve">random_effect_weight_percent</t>
   </si>
   <si>
+    <t xml:space="preserve">effect_input_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">events_exposed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_exposed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">events_control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oosterom-Eijmael 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multicenter, randomized, double-blind, placebo-controlled superiority trial (RCT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_dichotomous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snel 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prospective, single-center, open-label, phase IV, randomized, parallel-group controlled pilot trial (1:1). Intention-to-treat analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Li 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Randomized, open-label, blinded-endpoint trial (mITT analysis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reported_effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruste 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-centre retrospective cohort with overlap-weighted propensity score causal analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolland 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-center retrospective cohort with causal inference weighting (entropy balancing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitta 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-center, investigator-initiated, pragmatic, randomized, open-label trial with blinded outcome adjudication (modified intention-to-treat analysis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-center, randomized, open-label trial with blinded outcome adjudication; modified intention-to-treat analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-center, open-label, phase IV randomized controlled pilot study; intention-to-treat analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multicenter, double-blind, placebo-controlled randomized clinical trial; primary intention-to-treat analysis with post hoc creatinine-only analysis</t>
+  </si>
+  <si>
     <t xml:space="preserve">dataset_path</t>
   </si>
   <si>
@@ -107,46 +261,100 @@
     <t xml:space="preserve">status</t>
   </si>
   <si>
-    <t xml:space="preserve">error_message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">additional_analysis_meta_analysis_ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/additional_analysis/AA_20260814_133034_creatinine_only_aki_sensitivity_analysis/additional_analysis_meta_analysis_ready.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plot.new has not been called yet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/additional_analysis/AA_20260814_143238_creatinine_only_aki_sensitivity_analysis/additional_analysis_meta_analysis_ready.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No complete positive effect-size rows were available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meta_analysis_ready_primary_rct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_primary_rct.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixed effect measures detected in one analysis dataset: 64, RISK RATIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meta_analysis_ready_secondary_observational</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_secondary_observational.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixed effect measures detected in one analysis dataset: RELATIVE RISK, RISK RATIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meta_analysis_ready_sensitivity_rct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_sensitivity_rct.csv</t>
+    <t xml:space="preserve">PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first_author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">publication_year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">screening_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oosterom-Eijmael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/extraction/study_characteristics_agent.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Li</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCT04523064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USER REQUIRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dutch Trial Register 52118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCT05590143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST-CABGDM (Pitta et al., 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snel et al. randomized pilot study (2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCURI-2 (Oosterom-Eijmael et al., 2026)</t>
   </si>
 </sst>
 </file>
@@ -527,6 +735,278 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.586329397793633</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.146628989365185</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.34457158987056</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.239296661657056</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.818601640760815</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.226982990478109</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.0254580492808</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.00403508050962424</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.844315003620808</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0218403275763526</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32.6399786288488</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.661441788909137</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.810201301028674</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.134106098931173</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.26874001465668</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0217117223277289</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.596686774280369</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.296157008068087</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.20218362862195</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.100681609896476</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.728256768335757</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.119180036829702</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11.0398333810452</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0115124199044159</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>37</v>
+      </c>
+      <c r="U4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.717480763901209</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.30613566432356</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.68153765326795</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.235496766861311</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.37045428490306</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0617447429770707</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.17689399203048</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.204242555065259</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U5" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -544,34 +1024,695 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.541463414634146</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.450596009025557</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.650655184499516</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.613479777826074</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0937284213735102</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40.2696689264537</v>
+      </c>
+      <c r="K2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" t="n">
+        <v>111</v>
+      </c>
+      <c r="M2" t="n">
+        <v>392</v>
+      </c>
+      <c r="N2" t="n">
+        <v>205</v>
+      </c>
+      <c r="O2" t="n">
+        <v>392</v>
+      </c>
+      <c r="P2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.131627455471535</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.683747928405886</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1.20397280432594</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.420317340430616</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.5211387782931</v>
+      </c>
+      <c r="K3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" t="n">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="O3" t="n">
+        <v>30</v>
+      </c>
+      <c r="P3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="E4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.685301100894208</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.43017426751705</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.0100503358535015</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.187680304841516</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36.2091922952532</v>
+      </c>
+      <c r="K4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.804636642581399</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.55896454824092</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.113328685307003</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.168724102613614</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50.8905247591405</v>
+      </c>
+      <c r="K5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.438075626822918</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.90600794862399</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.462035459596559</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.18537496749964</v>
+      </c>
+      <c r="J6" t="n">
+        <v>49.1094752408595</v>
+      </c>
+      <c r="K6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.541463414634146</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.450596009025557</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.650655184499516</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.613479777826074</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0937284213735102</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.0143808663438</v>
+      </c>
+      <c r="K7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" t="n">
+        <v>111</v>
+      </c>
+      <c r="M7" t="n">
+        <v>392</v>
+      </c>
+      <c r="N7" t="n">
+        <v>205</v>
+      </c>
+      <c r="O7" t="n">
+        <v>392</v>
+      </c>
+      <c r="P7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.131627455471535</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.683747928405886</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1.20397280432594</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.420317340430616</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14.7125251902173</v>
+      </c>
+      <c r="K8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
-        <v>14</v>
+      <c r="N8" t="n">
+        <v>20</v>
+      </c>
+      <c r="O8" t="n">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.685301100894208</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.43017426751705</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.0100503358535015</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.187680304841516</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.1900335995043</v>
+      </c>
+      <c r="K9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.575036425449247</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.343147234167119</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.963629770748514</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.553321891583838</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.263409829097023</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23.0830603439346</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" t="n">
+        <v>16</v>
+      </c>
+      <c r="M10" t="n">
+        <v>71</v>
+      </c>
+      <c r="N10" t="n">
+        <v>29</v>
+      </c>
+      <c r="O10" t="n">
+        <v>74</v>
+      </c>
+      <c r="P10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.339221085367519</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.957782443411488</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.562118918153541</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.264792772156039</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.861801718552</v>
+      </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16</v>
+      </c>
+      <c r="M11" t="n">
+        <v>71</v>
+      </c>
+      <c r="N11" t="n">
+        <v>29</v>
+      </c>
+      <c r="O11" t="n">
+        <v>74</v>
+      </c>
+      <c r="P11" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.133369292051001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.51834051816488</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.798507696217772</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.620483682299543</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.8800284687193</v>
+      </c>
+      <c r="K12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>30</v>
+      </c>
+      <c r="P12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.657613494416894</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.31521023723351</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.0725706928348354</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.176823260346925</v>
+      </c>
+      <c r="J13" t="n">
+        <v>52.2581698127286</v>
+      </c>
+      <c r="K13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" t="n">
+        <v>53</v>
+      </c>
+      <c r="M13" t="n">
+        <v>392</v>
+      </c>
+      <c r="N13" t="n">
+        <v>57</v>
+      </c>
+      <c r="O13" t="n">
+        <v>392</v>
+      </c>
+      <c r="P13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -590,16 +1731,129 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="D1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F2" t="s">
         <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -618,66 +1872,323 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
       <c r="C4" t="s">
-        <v>38</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
